--- a/导入示例/example_img.xlsx
+++ b/导入示例/example_img.xlsx
@@ -1367,27 +1367,27 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="67.25" spans="2:5">
-      <c r="B3" t="str">
-        <f>_xlfn.DISPIMG("ID_E3102AF747AC4E31A1B9D05DA8190E8E",1)</f>
-        <v>=DISPIMG("ID_E3102AF747AC4E31A1B9D05DA8190E8E",1)</v>
-      </c>
-      <c r="C3" t="str">
-        <f>_xlfn.DISPIMG("ID_1E11818E7AC84719AC71E6D717EC4D25",1)</f>
-        <v>=DISPIMG("ID_1E11818E7AC84719AC71E6D717EC4D25",1)</v>
-      </c>
-      <c r="D3" t="str">
-        <f>_xlfn.DISPIMG("ID_76587A98D310449DB8EFF324F764F561",1)</f>
-        <v>=DISPIMG("ID_76587A98D310449DB8EFF324F764F561",1)</v>
-      </c>
-      <c r="E3" t="str">
-        <f>_xlfn.DISPIMG("ID_E11D033B118B4DD8B52DD03EF18F9470",1)</f>
-        <v>=DISPIMG("ID_E11D033B118B4DD8B52DD03EF18F9470",1)</v>
-      </c>
+    <row r="3" ht="67.25" spans="1:6">
       <c r="A3" t="inlineStr">
         <is>
           <t>Which graph represents the equation y = x?</t>
         </is>
+      </c>
+      <c r="B3" t="str">
+        <f>_xlfn.DISPIMG("ID_E3102AF747AC4E31A1B9D05DA8190E8E",1)</f>
+        <v>=DISPIMG("ID_E3102AF747AC4E31A1B9D05DA8190E8E",1)</v>
+      </c>
+      <c r="C3" t="str">
+        <f>_xlfn.DISPIMG("ID_1E11818E7AC84719AC71E6D717EC4D25",1)</f>
+        <v>=DISPIMG("ID_1E11818E7AC84719AC71E6D717EC4D25",1)</v>
+      </c>
+      <c r="D3" t="str">
+        <f>_xlfn.DISPIMG("ID_76587A98D310449DB8EFF324F764F561",1)</f>
+        <v>=DISPIMG("ID_76587A98D310449DB8EFF324F764F561",1)</v>
+      </c>
+      <c r="E3" t="str">
+        <f>_xlfn.DISPIMG("ID_E11D033B118B4DD8B52DD03EF18F9470",1)</f>
+        <v>=DISPIMG("ID_E11D033B118B4DD8B52DD03EF18F9470",1)</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>

--- a/导入示例/example_img.xlsx
+++ b/导入示例/example_img.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12975"/>
+    <workbookView windowWidth="27810" windowHeight="12495"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,141 +27,16 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="ID_D216F3ABF5F142E3AB23EB2AF5DA8B06" descr="img1"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="4267200" cy="3200400"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="ID_E3102AF747AC4E31A1B9D05DA8190E8E" descr="img2"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="4076700" cy="3276600"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="ID_1E11818E7AC84719AC71E6D717EC4D25" descr="img3"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="4229100" cy="3314700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="ID_76587A98D310449DB8EFF324F764F561" descr="img4"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="4191000" cy="3238500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-  <etc:cellImage>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="ID_E11D033B118B4DD8B52DD03EF18F9470" descr="img5"/>
-        <xdr:cNvPicPr/>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="3695700" cy="3314700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-  </etc:cellImage>
-</etc:cellImages>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+  <si>
+    <t>年份</t>
+  </si>
   <si>
     <t>题目</t>
-  </si>
-  <si>
-    <t>选项A</t>
-  </si>
-  <si>
-    <t>选项B</t>
-  </si>
-  <si>
-    <t>选项C</t>
-  </si>
-  <si>
-    <t>选项D</t>
   </si>
   <si>
     <t>正确答案</t>
@@ -1307,16 +1182,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="2" outlineLevelCol="5"/>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="14.5" customWidth="1"/>
-    <col min="2" max="5" width="12.5"/>
+    <col min="2" max="2" width="17.25" customWidth="1"/>
+    <col min="3" max="3" width="11.5" customWidth="1"/>
+    <col min="4" max="5" width="12.5"/>
+    <col min="6" max="6" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1326,75 +1203,8 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" ht="75" customHeight="1" spans="1:1">
-      <c r="A2" t="str">
-        <f>_xlfn.DISPIMG("ID_D216F3ABF5F142E3AB23EB2AF5DA8B06",1)</f>
-        <v>=DISPIMG("ID_D216F3ABF5F142E3AB23EB2AF5DA8B06",1)</v>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>positive gradient and positive y-intercept</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>positive gradient and negative y-intercept</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>negative gradient and positive y-intercept</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>negative gradient and negative y-intercept</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="67.25" spans="1:6">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Which graph represents the equation y = x?</t>
-        </is>
-      </c>
-      <c r="B3" t="str">
-        <f>_xlfn.DISPIMG("ID_E3102AF747AC4E31A1B9D05DA8190E8E",1)</f>
-        <v>=DISPIMG("ID_E3102AF747AC4E31A1B9D05DA8190E8E",1)</v>
-      </c>
-      <c r="C3" t="str">
-        <f>_xlfn.DISPIMG("ID_1E11818E7AC84719AC71E6D717EC4D25",1)</f>
-        <v>=DISPIMG("ID_1E11818E7AC84719AC71E6D717EC4D25",1)</v>
-      </c>
-      <c r="D3" t="str">
-        <f>_xlfn.DISPIMG("ID_76587A98D310449DB8EFF324F764F561",1)</f>
-        <v>=DISPIMG("ID_76587A98D310449DB8EFF324F764F561",1)</v>
-      </c>
-      <c r="E3" t="str">
-        <f>_xlfn.DISPIMG("ID_E11D033B118B4DD8B52DD03EF18F9470",1)</f>
-        <v>=DISPIMG("ID_E11D033B118B4DD8B52DD03EF18F9470",1)</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-    </row>
+    <row r="2" ht="75" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/导入示例/example_img.xlsx
+++ b/导入示例/example_img.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27810" windowHeight="12495"/>
+    <workbookView windowWidth="28800" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,19 +27,122 @@
 </file>
 
 <file path=xl/cellimages.xml><?xml version="1.0" encoding="utf-8"?>
-<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData"/>
+<etc:cellImages xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="ID_5A1291E2ED744D318E0DAD58817F0344"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1209675" y="190500"/>
+          <a:ext cx="1714500" cy="1381125"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="ID_14A640D3F5F94ECB8B40D5C80769BBE6"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1895475" y="1143000"/>
+          <a:ext cx="1943100" cy="1295400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+  <etc:cellImage>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="ID_E945DB216B7A4DC5B35C201AEF75571C"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1895475" y="2028825"/>
+          <a:ext cx="1971675" cy="2238375"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+  </etc:cellImage>
+</etc:cellImages>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
-    <t>年份</t>
+    <t>来源</t>
   </si>
   <si>
     <t>题目</t>
   </si>
   <si>
     <t>正确答案</t>
+  </si>
+  <si>
+    <t>[DSE 2012 MT I (2)]</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>[DSE 2015 MT Ⅱ (1)]</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>[DSE 2018 MT II (4)]</t>
   </si>
 </sst>
 </file>
@@ -1184,9 +1287,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" outlineLevelCol="2"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
+    <col min="1" max="1" width="24.875" customWidth="1"/>
     <col min="2" max="2" width="17.25" customWidth="1"/>
     <col min="3" max="3" width="11.5" customWidth="1"/>
     <col min="4" max="5" width="12.5"/>
@@ -1204,7 +1308,42 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="75" customHeight="1"/>
+    <row r="2" ht="75" customHeight="1" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="str">
+        <f>_xlfn.DISPIMG("ID_5A1291E2ED744D318E0DAD58817F0344",1)</f>
+        <v>=DISPIMG("ID_5A1291E2ED744D318E0DAD58817F0344",1)</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" ht="69.75" spans="1:3">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="str">
+        <f>_xlfn.DISPIMG("ID_14A640D3F5F94ECB8B40D5C80769BBE6",1)</f>
+        <v>=DISPIMG("ID_14A640D3F5F94ECB8B40D5C80769BBE6",1)</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" ht="117.15" spans="1:3">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="str">
+        <f>_xlfn.DISPIMG("ID_E945DB216B7A4DC5B35C201AEF75571C",1)</f>
+        <v>=DISPIMG("ID_E945DB216B7A4DC5B35C201AEF75571C",1)</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
